--- a/data/dividends_info_20261025.xlsx
+++ b/data/dividends_info_20261025.xlsx
@@ -2490,7 +2490,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2534,14 +2534,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2602,14 +2602,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2728,7 +2728,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2755,14 +2755,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2772,14 +2772,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2796,7 +2796,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2830,7 +2830,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2847,7 +2847,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2857,14 +2857,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2898,7 +2898,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2932,7 +2932,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3034,7 +3034,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3051,7 +3051,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3197,14 +3197,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3214,14 +3214,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3272,7 +3272,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3306,7 +3306,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3323,7 +3323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3357,7 +3357,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3367,14 +3367,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3435,14 +3435,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3561,7 +3561,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3595,7 +3595,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3605,14 +3605,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3622,14 +3622,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3639,14 +3639,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3656,14 +3656,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3707,14 +3707,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3731,7 +3731,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3748,7 +3748,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3765,7 +3765,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3799,7 +3799,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3816,7 +3816,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3826,14 +3826,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3867,7 +3867,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3884,7 +3884,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3894,14 +3894,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3918,7 +3918,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3928,14 +3928,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3969,7 +3969,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3979,14 +3979,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4003,7 +4003,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4020,7 +4020,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4030,14 +4030,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4088,7 +4088,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4105,7 +4105,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4122,7 +4122,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4132,14 +4132,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4156,7 +4156,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4166,14 +4166,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4183,14 +4183,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4207,7 +4207,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4224,7 +4224,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4234,14 +4234,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4258,7 +4258,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4336,14 +4336,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4394,7 +4394,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4404,14 +4404,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4428,7 +4428,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4445,7 +4445,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4462,7 +4462,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4547,7 +4547,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4557,14 +4557,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4574,14 +4574,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4615,7 +4615,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4649,7 +4649,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4676,14 +4676,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4819,7 +4819,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4853,7 +4853,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4870,7 +4870,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4880,14 +4880,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4904,7 +4904,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4921,7 +4921,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4938,7 +4938,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4955,7 +4955,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4972,7 +4972,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5006,7 +5006,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5040,7 +5040,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5101,14 +5101,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5125,7 +5125,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5152,14 +5152,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5176,7 +5176,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5210,7 +5210,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5220,14 +5220,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5244,7 +5244,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5254,14 +5254,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5295,7 +5295,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5431,7 +5431,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5441,14 +5441,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5458,14 +5458,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5509,14 +5509,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5567,7 +5567,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5707,95 +5707,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Lindbergh S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OPS Retail S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>